--- a/output/graficos_nacionales/plot_nacional_m_miginterna_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_miginterna_a_2019.xlsx
@@ -16233,7 +16233,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Migración interna neta</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_m_miginterna_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_miginterna_a_2019.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="734">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:20</t>
+    <t xml:space="preserve">2026-07-30 15:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2185,16 +2185,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_nacional_m_miginterna_a_2019.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Migracion interna neta</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Comuna (vista nacional macrozonal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019</t>
   </si>
   <si>
     <t xml:space="preserve">variable</t>
@@ -13647,23 +13656,23 @@
         <v>723</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
     </row>
   </sheetData>
@@ -13685,21 +13694,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13708,7 +13717,7 @@
         <v>2019</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_m_miginterna_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_miginterna_a_2019.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Macrozona Austral</t>
   </si>
   <si>
-    <t xml:space="preserve">value</t>
+    <t xml:space="preserve">Valor (por 1.000)</t>
   </si>
   <si>
     <t xml:space="preserve">12104</t>
@@ -256,18 +256,18 @@
     <t xml:space="preserve">San Felipe</t>
   </si>
   <si>
+    <t xml:space="preserve">5403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papudo</t>
+  </si>
+  <si>
     <t xml:space="preserve">7201</t>
   </si>
   <si>
     <t xml:space="preserve">Cauquenes</t>
   </si>
   <si>
-    <t xml:space="preserve">5403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papudo</t>
-  </si>
-  <si>
     <t xml:space="preserve">6203</t>
   </si>
   <si>
@@ -349,18 +349,18 @@
     <t xml:space="preserve">Coltauco</t>
   </si>
   <si>
+    <t xml:space="preserve">13302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lampa</t>
+  </si>
+  <si>
     <t xml:space="preserve">7402</t>
   </si>
   <si>
     <t xml:space="preserve">Colbún</t>
   </si>
   <si>
-    <t xml:space="preserve">13302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lampa</t>
-  </si>
-  <si>
     <t xml:space="preserve">13114</t>
   </si>
   <si>
@@ -463,18 +463,18 @@
     <t xml:space="preserve">La Cisterna</t>
   </si>
   <si>
+    <t xml:space="preserve">13604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Padre Hurtado</t>
+  </si>
+  <si>
     <t xml:space="preserve">7305</t>
   </si>
   <si>
     <t xml:space="preserve">Rauco</t>
   </si>
   <si>
-    <t xml:space="preserve">13604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Padre Hurtado</t>
-  </si>
-  <si>
     <t xml:space="preserve">5601</t>
   </si>
   <si>
@@ -511,16 +511,22 @@
     <t xml:space="preserve">Valparaíso</t>
   </si>
   <si>
+    <t xml:space="preserve">5502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calera</t>
+  </si>
+  <si>
     <t xml:space="preserve">7401</t>
   </si>
   <si>
     <t xml:space="preserve">Linares</t>
   </si>
   <si>
-    <t xml:space="preserve">5502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calera</t>
+    <t xml:space="preserve">5804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villa Alemana</t>
   </si>
   <si>
     <t xml:space="preserve">13103</t>
@@ -529,12 +535,6 @@
     <t xml:space="preserve">Cerro Navia</t>
   </si>
   <si>
-    <t xml:space="preserve">5804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Villa Alemana</t>
-  </si>
-  <si>
     <t xml:space="preserve">13119</t>
   </si>
   <si>
@@ -553,36 +553,36 @@
     <t xml:space="preserve">Romeral</t>
   </si>
   <si>
+    <t xml:space="preserve">13129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Joaquín</t>
+  </si>
+  <si>
     <t xml:space="preserve">7104</t>
   </si>
   <si>
     <t xml:space="preserve">Empedrado</t>
   </si>
   <si>
-    <t xml:space="preserve">13129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Joaquín</t>
-  </si>
-  <si>
     <t xml:space="preserve">6117</t>
   </si>
   <si>
     <t xml:space="preserve">San Vicente</t>
   </si>
   <si>
+    <t xml:space="preserve">5401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Ligua</t>
+  </si>
+  <si>
     <t xml:space="preserve">7309</t>
   </si>
   <si>
     <t xml:space="preserve">Vichuquén</t>
   </si>
   <si>
-    <t xml:space="preserve">5401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Ligua</t>
-  </si>
-  <si>
     <t xml:space="preserve">6108</t>
   </si>
   <si>
@@ -631,18 +631,18 @@
     <t xml:space="preserve">Las Cabras</t>
   </si>
   <si>
+    <t xml:space="preserve">13105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Bosque</t>
+  </si>
+  <si>
     <t xml:space="preserve">6101</t>
   </si>
   <si>
     <t xml:space="preserve">Rancagua</t>
   </si>
   <si>
-    <t xml:space="preserve">13105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Bosque</t>
-  </si>
-  <si>
     <t xml:space="preserve">6205</t>
   </si>
   <si>
@@ -709,18 +709,18 @@
     <t xml:space="preserve">Longaví</t>
   </si>
   <si>
+    <t xml:space="preserve">5702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catemu</t>
+  </si>
+  <si>
     <t xml:space="preserve">7109</t>
   </si>
   <si>
     <t xml:space="preserve">San Clemente</t>
   </si>
   <si>
-    <t xml:space="preserve">5702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catemu</t>
-  </si>
-  <si>
     <t xml:space="preserve">6310</t>
   </si>
   <si>
@@ -781,18 +781,18 @@
     <t xml:space="preserve">Talca</t>
   </si>
   <si>
+    <t xml:space="preserve">13602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Monte</t>
+  </si>
+  <si>
     <t xml:space="preserve">7102</t>
   </si>
   <si>
     <t xml:space="preserve">Constitución</t>
   </si>
   <si>
-    <t xml:space="preserve">13602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Monte</t>
-  </si>
-  <si>
     <t xml:space="preserve">13503</t>
   </si>
   <si>
@@ -811,24 +811,24 @@
     <t xml:space="preserve">Quinta de Tilcoco</t>
   </si>
   <si>
+    <t xml:space="preserve">5506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puente Alto</t>
+  </si>
+  <si>
     <t xml:space="preserve">7202</t>
   </si>
   <si>
     <t xml:space="preserve">Chanco</t>
   </si>
   <si>
-    <t xml:space="preserve">13201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puente Alto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogales</t>
-  </si>
-  <si>
     <t xml:space="preserve">13126</t>
   </si>
   <si>
@@ -877,18 +877,18 @@
     <t xml:space="preserve">Codegua</t>
   </si>
   <si>
+    <t xml:space="preserve">6109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malloa</t>
+  </si>
+  <si>
     <t xml:space="preserve">7103</t>
   </si>
   <si>
     <t xml:space="preserve">Curepto</t>
   </si>
   <si>
-    <t xml:space="preserve">6109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malloa</t>
-  </si>
-  <si>
     <t xml:space="preserve">13303</t>
   </si>
   <si>
@@ -955,18 +955,18 @@
     <t xml:space="preserve">Coinco</t>
   </si>
   <si>
+    <t xml:space="preserve">5103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concón</t>
+  </si>
+  <si>
     <t xml:space="preserve">13125</t>
   </si>
   <si>
     <t xml:space="preserve">Quilicura</t>
   </si>
   <si>
-    <t xml:space="preserve">5103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concón</t>
-  </si>
-  <si>
     <t xml:space="preserve">13132</t>
   </si>
   <si>
@@ -1009,18 +1009,18 @@
     <t xml:space="preserve">Hualañé</t>
   </si>
   <si>
+    <t xml:space="preserve">7110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Rafael</t>
+  </si>
+  <si>
     <t xml:space="preserve">16101</t>
   </si>
   <si>
     <t xml:space="preserve">Chillán</t>
   </si>
   <si>
-    <t xml:space="preserve">7110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Rafael</t>
-  </si>
-  <si>
     <t xml:space="preserve">5606</t>
   </si>
   <si>
@@ -1375,18 +1375,18 @@
     <t xml:space="preserve">Illapel</t>
   </si>
   <si>
+    <t xml:space="preserve">15101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arica</t>
+  </si>
+  <si>
     <t xml:space="preserve">2104</t>
   </si>
   <si>
     <t xml:space="preserve">Taltal</t>
   </si>
   <si>
-    <t xml:space="preserve">15101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arica</t>
-  </si>
-  <si>
     <t xml:space="preserve">4203</t>
   </si>
   <si>
@@ -1735,18 +1735,18 @@
     <t xml:space="preserve">Renaico</t>
   </si>
   <si>
+    <t xml:space="preserve">9107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorbea</t>
+  </si>
+  <si>
     <t xml:space="preserve">10305</t>
   </si>
   <si>
     <t xml:space="preserve">Río Negro</t>
   </si>
   <si>
-    <t xml:space="preserve">9107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorbea</t>
-  </si>
-  <si>
     <t xml:space="preserve">8105</t>
   </si>
   <si>
@@ -1777,24 +1777,24 @@
     <t xml:space="preserve">Lautaro</t>
   </si>
   <si>
+    <t xml:space="preserve">8107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pucón</t>
+  </si>
+  <si>
     <t xml:space="preserve">10401</t>
   </si>
   <si>
     <t xml:space="preserve">Chaitén</t>
   </si>
   <si>
-    <t xml:space="preserve">8107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pucón</t>
-  </si>
-  <si>
     <t xml:space="preserve">9201</t>
   </si>
   <si>
@@ -1831,18 +1831,18 @@
     <t xml:space="preserve">Arauco</t>
   </si>
   <si>
+    <t xml:space="preserve">8203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cañete</t>
+  </si>
+  <si>
     <t xml:space="preserve">9103</t>
   </si>
   <si>
     <t xml:space="preserve">Cunco</t>
   </si>
   <si>
-    <t xml:space="preserve">8203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cañete</t>
-  </si>
-  <si>
     <t xml:space="preserve">14103</t>
   </si>
   <si>
@@ -1867,24 +1867,24 @@
     <t xml:space="preserve">Santa Bárbara</t>
   </si>
   <si>
+    <t xml:space="preserve">8106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Rosendo</t>
+  </si>
+  <si>
     <t xml:space="preserve">9113</t>
   </si>
   <si>
     <t xml:space="preserve">Perquenco</t>
   </si>
   <si>
-    <t xml:space="preserve">8106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Rosendo</t>
-  </si>
-  <si>
     <t xml:space="preserve">8204</t>
   </si>
   <si>
@@ -1903,18 +1903,18 @@
     <t xml:space="preserve">Calbuco</t>
   </si>
   <si>
+    <t xml:space="preserve">14108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panguipulli</t>
+  </si>
+  <si>
     <t xml:space="preserve">10202</t>
   </si>
   <si>
     <t xml:space="preserve">Ancud</t>
   </si>
   <si>
-    <t xml:space="preserve">14108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Panguipulli</t>
-  </si>
-  <si>
     <t xml:space="preserve">10105</t>
   </si>
   <si>
@@ -1939,18 +1939,18 @@
     <t xml:space="preserve">Nacimiento</t>
   </si>
   <si>
+    <t xml:space="preserve">9211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victoria</t>
+  </si>
+  <si>
     <t xml:space="preserve">14204</t>
   </si>
   <si>
     <t xml:space="preserve">Río Bueno</t>
   </si>
   <si>
-    <t xml:space="preserve">9211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victoria</t>
-  </si>
-  <si>
     <t xml:space="preserve">10307</t>
   </si>
   <si>
@@ -2005,18 +2005,18 @@
     <t xml:space="preserve">Tirúa</t>
   </si>
   <si>
+    <t xml:space="preserve">9206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Sauces</t>
+  </si>
+  <si>
     <t xml:space="preserve">14106</t>
   </si>
   <si>
     <t xml:space="preserve">Mariquina</t>
   </si>
   <si>
-    <t xml:space="preserve">9206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Sauces</t>
-  </si>
-  <si>
     <t xml:space="preserve">10203</t>
   </si>
   <si>
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:27</t>
+    <t xml:space="preserve">2026-09-08 10:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2590,9 +2590,9 @@
     <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="19.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="12.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="19.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="10.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="14.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="19.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3592,10 +3592,10 @@
         <v>2019</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>79</v>
@@ -3624,10 +3624,10 @@
         <v>2019</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>81</v>
@@ -4072,10 +4072,10 @@
         <v>2019</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>110</v>
@@ -4104,10 +4104,10 @@
         <v>2019</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>112</v>
@@ -4680,10 +4680,10 @@
         <v>2019</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>148</v>
@@ -4712,10 +4712,10 @@
         <v>2019</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>150</v>
@@ -4936,10 +4936,10 @@
         <v>2019</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>164</v>
@@ -4968,10 +4968,10 @@
         <v>2019</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>166</v>
@@ -5000,10 +5000,10 @@
         <v>2019</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>168</v>
@@ -5032,10 +5032,10 @@
         <v>2019</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>170</v>
@@ -5160,10 +5160,10 @@
         <v>2019</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>178</v>
@@ -5192,10 +5192,10 @@
         <v>2019</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>180</v>
@@ -5256,10 +5256,10 @@
         <v>2019</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>184</v>
@@ -5288,10 +5288,10 @@
         <v>2019</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>186</v>
@@ -5576,10 +5576,10 @@
         <v>2019</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>204</v>
@@ -5608,10 +5608,10 @@
         <v>2019</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>206</v>
@@ -5992,10 +5992,10 @@
         <v>2019</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>230</v>
@@ -6024,10 +6024,10 @@
         <v>2019</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>232</v>
@@ -6376,10 +6376,10 @@
         <v>2019</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>254</v>
@@ -6408,10 +6408,10 @@
         <v>2019</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>256</v>
@@ -6536,10 +6536,10 @@
         <v>2019</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>264</v>
@@ -6600,10 +6600,10 @@
         <v>2019</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>268</v>
@@ -6888,10 +6888,10 @@
         <v>2019</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>286</v>
@@ -6920,10 +6920,10 @@
         <v>2019</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>288</v>
@@ -7304,10 +7304,10 @@
         <v>2019</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>312</v>
@@ -7336,10 +7336,10 @@
         <v>2019</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>314</v>
@@ -7592,10 +7592,10 @@
         <v>2019</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>330</v>
@@ -7624,10 +7624,10 @@
         <v>2019</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>332</v>
@@ -9448,10 +9448,10 @@
         <v>2019</v>
       </c>
       <c r="B215" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>452</v>
@@ -9480,10 +9480,10 @@
         <v>2019</v>
       </c>
       <c r="B216" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>454</v>
@@ -11304,10 +11304,10 @@
         <v>2019</v>
       </c>
       <c r="B273" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>572</v>
@@ -11336,10 +11336,10 @@
         <v>2019</v>
       </c>
       <c r="B274" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>574</v>
@@ -11528,10 +11528,10 @@
         <v>2019</v>
       </c>
       <c r="B280" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>586</v>
@@ -11560,10 +11560,10 @@
         <v>2019</v>
       </c>
       <c r="B281" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>588</v>
@@ -11592,10 +11592,10 @@
         <v>2019</v>
       </c>
       <c r="B282" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="D282" s="2" t="s">
         <v>590</v>
@@ -11816,10 +11816,10 @@
         <v>2019</v>
       </c>
       <c r="B289" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>604</v>
@@ -11848,10 +11848,10 @@
         <v>2019</v>
       </c>
       <c r="B290" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>606</v>
@@ -12008,10 +12008,10 @@
         <v>2019</v>
       </c>
       <c r="B295" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>616</v>
@@ -12072,10 +12072,10 @@
         <v>2019</v>
       </c>
       <c r="B297" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>620</v>
@@ -12200,10 +12200,10 @@
         <v>2019</v>
       </c>
       <c r="B301" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>497</v>
+        <v>540</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>628</v>
@@ -12232,10 +12232,10 @@
         <v>2019</v>
       </c>
       <c r="B302" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>540</v>
+        <v>497</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>630</v>
@@ -12392,10 +12392,10 @@
         <v>2019</v>
       </c>
       <c r="B307" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>540</v>
+        <v>507</v>
       </c>
       <c r="D307" s="2" t="s">
         <v>640</v>
@@ -12424,10 +12424,10 @@
         <v>2019</v>
       </c>
       <c r="B308" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>507</v>
+        <v>540</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>642</v>
@@ -12744,10 +12744,10 @@
         <v>2019</v>
       </c>
       <c r="B318" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>540</v>
+        <v>507</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>662</v>
@@ -12776,10 +12776,10 @@
         <v>2019</v>
       </c>
       <c r="B319" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>507</v>
+        <v>540</v>
       </c>
       <c r="D319" s="2" t="s">
         <v>664</v>
@@ -13687,7 +13687,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="19.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
   </cols>
